--- a/Codes/Trial 2/Trial2_LSTM_Leaders_Results.xlsx
+++ b/Codes/Trial 2/Trial2_LSTM_Leaders_Results.xlsx
@@ -470,13 +470,13 @@
         <v>2023</v>
       </c>
       <c r="C2" t="n">
-        <v>20.91</v>
+        <v>20.59</v>
       </c>
       <c r="D2" t="n">
-        <v>27.88341522216797</v>
+        <v>5.266295909881592</v>
       </c>
       <c r="E2" t="n">
-        <v>6.973415222167965</v>
+        <v>15.32370409011841</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -494,13 +494,13 @@
         <v>2024</v>
       </c>
       <c r="C3" t="n">
-        <v>18.57999999999999</v>
+        <v>29.38</v>
       </c>
       <c r="D3" t="n">
-        <v>33.94537734985352</v>
+        <v>9.183833122253418</v>
       </c>
       <c r="E3" t="n">
-        <v>15.36537734985352</v>
+        <v>20.19616687774658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -518,13 +518,13 @@
         <v>2023</v>
       </c>
       <c r="C4" t="n">
-        <v>20.59</v>
+        <v>4.39</v>
       </c>
       <c r="D4" t="n">
-        <v>27.13837623596191</v>
+        <v>7.662208080291748</v>
       </c>
       <c r="E4" t="n">
-        <v>6.548376235961911</v>
+        <v>3.272208080291748</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -542,13 +542,13 @@
         <v>2024</v>
       </c>
       <c r="C5" t="n">
-        <v>29.38</v>
+        <v>5.700000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>39.72025299072266</v>
+        <v>4.534398555755615</v>
       </c>
       <c r="E5" t="n">
-        <v>10.34025299072266</v>
+        <v>1.165601444244386</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -566,13 +566,13 @@
         <v>2023</v>
       </c>
       <c r="C6" t="n">
-        <v>4.39</v>
+        <v>37.23999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>30.04946899414062</v>
+        <v>4.013365745544434</v>
       </c>
       <c r="E6" t="n">
-        <v>25.65946899414062</v>
+        <v>33.22663425445556</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -590,13 +590,13 @@
         <v>2024</v>
       </c>
       <c r="C7" t="n">
-        <v>5.700000000000001</v>
+        <v>52.72000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>41.3839225769043</v>
+        <v>11.04000282287598</v>
       </c>
       <c r="E7" t="n">
-        <v>35.68392257690429</v>
+        <v>41.67999717712404</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         <v>2023</v>
       </c>
       <c r="C8" t="n">
-        <v>37.23999999999999</v>
+        <v>34.91</v>
       </c>
       <c r="D8" t="n">
-        <v>29.88569259643555</v>
+        <v>12.06189155578613</v>
       </c>
       <c r="E8" t="n">
-        <v>7.354307403564448</v>
+        <v>22.84810844421387</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -638,13 +638,13 @@
         <v>2024</v>
       </c>
       <c r="C9" t="n">
-        <v>52.72000000000001</v>
+        <v>30.53</v>
       </c>
       <c r="D9" t="n">
-        <v>39.43014144897461</v>
+        <v>10.40601825714111</v>
       </c>
       <c r="E9" t="n">
-        <v>13.2898585510254</v>
+        <v>20.12398174285889</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -662,13 +662,13 @@
         <v>2023</v>
       </c>
       <c r="C10" t="n">
-        <v>34.91</v>
+        <v>17.73</v>
       </c>
       <c r="D10" t="n">
-        <v>22.70468711853027</v>
+        <v>9.255125999450684</v>
       </c>
       <c r="E10" t="n">
-        <v>12.20531288146973</v>
+        <v>8.47487400054932</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         <v>2024</v>
       </c>
       <c r="C11" t="n">
-        <v>30.53</v>
+        <v>17.92</v>
       </c>
       <c r="D11" t="n">
-        <v>26.01523780822754</v>
+        <v>13.70783233642578</v>
       </c>
       <c r="E11" t="n">
-        <v>4.514762191772462</v>
+        <v>4.212167663574217</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -710,13 +710,13 @@
         <v>2023</v>
       </c>
       <c r="C12" t="n">
-        <v>17.73</v>
+        <v>19.28000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>38.07347869873047</v>
+        <v>7.186524391174316</v>
       </c>
       <c r="E12" t="n">
-        <v>20.34347869873046</v>
+        <v>12.09347560882569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -734,13 +734,13 @@
         <v>2024</v>
       </c>
       <c r="C13" t="n">
-        <v>17.92</v>
+        <v>14.47</v>
       </c>
       <c r="D13" t="n">
-        <v>50.35112380981445</v>
+        <v>8.052903175354004</v>
       </c>
       <c r="E13" t="n">
-        <v>32.43112380981445</v>
+        <v>6.417096824645997</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -758,13 +758,13 @@
         <v>2023</v>
       </c>
       <c r="C14" t="n">
-        <v>19.28000000000001</v>
+        <v>6.659999999999998</v>
       </c>
       <c r="D14" t="n">
-        <v>38.83726501464844</v>
+        <v>6.561325073242188</v>
       </c>
       <c r="E14" t="n">
-        <v>19.55726501464843</v>
+        <v>0.09867492675781087</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -782,13 +782,13 @@
         <v>2024</v>
       </c>
       <c r="C15" t="n">
-        <v>14.47</v>
+        <v>8.039999999999997</v>
       </c>
       <c r="D15" t="n">
-        <v>55.40159606933594</v>
+        <v>4.308168888092041</v>
       </c>
       <c r="E15" t="n">
-        <v>40.93159606933594</v>
+        <v>3.731831111907956</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -806,13 +806,13 @@
         <v>2023</v>
       </c>
       <c r="C16" t="n">
-        <v>6.659999999999998</v>
+        <v>5.23</v>
       </c>
       <c r="D16" t="n">
-        <v>26.71454048156738</v>
+        <v>2.387395143508911</v>
       </c>
       <c r="E16" t="n">
-        <v>20.05454048156739</v>
+        <v>2.842604856491089</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -830,13 +830,13 @@
         <v>2024</v>
       </c>
       <c r="C17" t="n">
-        <v>8.039999999999997</v>
+        <v>5.25</v>
       </c>
       <c r="D17" t="n">
-        <v>58.58169174194336</v>
+        <v>5.856960773468018</v>
       </c>
       <c r="E17" t="n">
-        <v>50.54169174194336</v>
+        <v>0.6069607734680176</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>2023</v>
       </c>
       <c r="C18" t="n">
-        <v>5.23</v>
+        <v>31.52</v>
       </c>
       <c r="D18" t="n">
-        <v>33.6419677734375</v>
+        <v>7.345406055450439</v>
       </c>
       <c r="E18" t="n">
-        <v>28.4119677734375</v>
+        <v>24.17459394454956</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -878,13 +878,13 @@
         <v>2024</v>
       </c>
       <c r="C19" t="n">
-        <v>5.25</v>
+        <v>35.45</v>
       </c>
       <c r="D19" t="n">
-        <v>37.5616569519043</v>
+        <v>12.40570259094238</v>
       </c>
       <c r="E19" t="n">
-        <v>32.3116569519043</v>
+        <v>23.04429740905762</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -902,13 +902,13 @@
         <v>2023</v>
       </c>
       <c r="C20" t="n">
-        <v>31.52</v>
+        <v>4.6</v>
       </c>
       <c r="D20" t="n">
-        <v>33.51198196411133</v>
+        <v>6.104023933410645</v>
       </c>
       <c r="E20" t="n">
-        <v>1.991981964111332</v>
+        <v>1.504023933410645</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -926,13 +926,13 @@
         <v>2024</v>
       </c>
       <c r="C21" t="n">
-        <v>35.45</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>48.544921875</v>
+        <v>4.241387844085693</v>
       </c>
       <c r="E21" t="n">
-        <v>13.094921875</v>
+        <v>0.2413878440856934</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -950,13 +950,13 @@
         <v>2023</v>
       </c>
       <c r="C22" t="n">
-        <v>4.6</v>
+        <v>11.53</v>
       </c>
       <c r="D22" t="n">
-        <v>29.32467079162598</v>
+        <v>4.081006526947021</v>
       </c>
       <c r="E22" t="n">
-        <v>24.72467079162598</v>
+        <v>7.448993473052983</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -974,13 +974,13 @@
         <v>2024</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>7.490000000000002</v>
       </c>
       <c r="D23" t="n">
-        <v>42.78360748291016</v>
+        <v>6.441811561584473</v>
       </c>
       <c r="E23" t="n">
-        <v>38.78360748291016</v>
+        <v>1.048188438415529</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -998,13 +998,13 @@
         <v>2023</v>
       </c>
       <c r="C24" t="n">
-        <v>11.53</v>
+        <v>6.779999999999998</v>
       </c>
       <c r="D24" t="n">
-        <v>27.49441337585449</v>
+        <v>3.538702487945557</v>
       </c>
       <c r="E24" t="n">
-        <v>15.96441337585449</v>
+        <v>3.241297512054442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1022,13 +1022,13 @@
         <v>2024</v>
       </c>
       <c r="C25" t="n">
-        <v>7.490000000000002</v>
+        <v>6.789999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>36.90861129760742</v>
+        <v>4.356107234954834</v>
       </c>
       <c r="E25" t="n">
-        <v>29.41861129760742</v>
+        <v>2.433892765045165</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1046,13 +1046,13 @@
         <v>2023</v>
       </c>
       <c r="C26" t="n">
-        <v>6.779999999999998</v>
+        <v>39.42</v>
       </c>
       <c r="D26" t="n">
-        <v>28.18582153320312</v>
+        <v>5.569271564483643</v>
       </c>
       <c r="E26" t="n">
-        <v>21.40582153320313</v>
+        <v>33.85072843551636</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1070,13 +1070,13 @@
         <v>2024</v>
       </c>
       <c r="C27" t="n">
-        <v>6.789999999999999</v>
+        <v>35.99000000000002</v>
       </c>
       <c r="D27" t="n">
-        <v>40.16053009033203</v>
+        <v>4.448737144470215</v>
       </c>
       <c r="E27" t="n">
-        <v>33.37053009033203</v>
+        <v>31.5412628555298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1094,13 +1094,13 @@
         <v>2023</v>
       </c>
       <c r="C28" t="n">
-        <v>39.42</v>
+        <v>3.87</v>
       </c>
       <c r="D28" t="n">
-        <v>34.60651016235352</v>
+        <v>0.9052820801734924</v>
       </c>
       <c r="E28" t="n">
-        <v>4.813489837646486</v>
+        <v>2.964717919826507</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1118,13 +1118,13 @@
         <v>2024</v>
       </c>
       <c r="C29" t="n">
-        <v>35.99000000000002</v>
+        <v>3.76</v>
       </c>
       <c r="D29" t="n">
-        <v>53.85747528076172</v>
+        <v>1.342039108276367</v>
       </c>
       <c r="E29" t="n">
-        <v>17.8674752807617</v>
+        <v>2.417960891723633</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
